--- a/data/trans_bre/P16A07-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P16A07-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,9; 7,97</t>
+          <t>3,93; 8,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,6; 11,45</t>
+          <t>6,45; 11,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,59; 9,71</t>
+          <t>4,64; 9,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,49; 8,98</t>
+          <t>3,55; 9,11</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>74,01; 255,27</t>
+          <t>80,98; 255,83</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,76; 276,04</t>
+          <t>96,15; 293,26</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,44; 309,77</t>
+          <t>80,52; 288,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>38,29; 184,22</t>
+          <t>40,19; 179,67</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,33; 4,63</t>
+          <t>2,32; 4,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,79; 4,42</t>
+          <t>1,7; 4,52</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,06; 5,56</t>
+          <t>2,93; 5,6</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,49; 4,92</t>
+          <t>1,61; 5,03</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>161,31; 618,19</t>
+          <t>158,32; 644,96</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>58,36; 228,39</t>
+          <t>51,87; 222,67</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>117,13; 362,1</t>
+          <t>124,13; 379,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>48,99; 235,18</t>
+          <t>52,32; 236,25</t>
         </is>
       </c>
     </row>
@@ -860,7 +860,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 3,63</t>
+          <t>-0,39; 3,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -870,32 +870,32 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,73; 3,84</t>
+          <t>0,74; 3,93</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 3,29</t>
+          <t>-0,17; 3,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-19,97; 295,19</t>
+          <t>-18,3; 286,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-64,26; 272,9</t>
+          <t>-69,39; 264,91</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,47; 1792,09</t>
+          <t>16,2; 1824,89</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-13,6; 224,66</t>
+          <t>-9,19; 228,05</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,32; 5,34</t>
+          <t>3,38; 5,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,11; 6,38</t>
+          <t>4,06; 6,43</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,78; 5,96</t>
+          <t>3,8; 5,82</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,62; 5,05</t>
+          <t>2,45; 5,11</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>130,75; 301,93</t>
+          <t>131,42; 291,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>110,43; 241,87</t>
+          <t>113,25; 240,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>145,74; 329,14</t>
+          <t>146,19; 314,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>74,03; 187,9</t>
+          <t>69,44; 194,28</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P16A07-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P16A07-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6,36</t>
+          <t>6,96</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>111,42%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,93; 8,01</t>
+          <t>3,86; 8,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,45; 11,61</t>
+          <t>6,87; 11,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,64; 9,7</t>
+          <t>4,27; 9,36</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,55; 9,11</t>
+          <t>4,02; 9,36</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>80,98; 255,83</t>
+          <t>74,42; 246,23</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,15; 293,26</t>
+          <t>101,81; 298,42</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,52; 288,91</t>
+          <t>73,45; 290,15</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>40,19; 179,67</t>
+          <t>47,76; 194,68</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,43</t>
+          <t>3,69</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>124,15%</t>
+          <t>115,86%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,32; 4,54</t>
+          <t>2,37; 4,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,7; 4,52</t>
+          <t>1,83; 4,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,93; 5,6</t>
+          <t>3,02; 5,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,61; 5,03</t>
+          <t>2,62; 5,01</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>158,32; 644,96</t>
+          <t>158,36; 642,8</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>51,87; 222,67</t>
+          <t>59,1; 233,1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>124,13; 379,76</t>
+          <t>123,6; 378,04</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>52,32; 236,25</t>
+          <t>68,63; 190,3</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,61</t>
+          <t>1,75</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>73,0%</t>
+          <t>85,21%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 3,81</t>
+          <t>-0,4; 3,69</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 2,16</t>
+          <t>-1,88; 2,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,74; 3,93</t>
+          <t>0,82; 3,79</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 3,31</t>
+          <t>0,11; 3,39</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-18,3; 286,01</t>
+          <t>-20,68; 286,96</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-69,39; 264,91</t>
+          <t>-69,2; 282,99</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,2; 1824,89</t>
+          <t>50,13; 2150,75</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-9,19; 228,05</t>
+          <t>-3,45; 273,83</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3,93</t>
+          <t>4,21</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>121,32%</t>
+          <t>121,58%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,38; 5,25</t>
+          <t>3,29; 5,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,06; 6,43</t>
+          <t>4,16; 6,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,8; 5,82</t>
+          <t>3,77; 5,82</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,45; 5,11</t>
+          <t>3,27; 5,23</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>131,42; 291,01</t>
+          <t>125,11; 288,95</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>113,25; 240,46</t>
+          <t>114,72; 249,78</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>146,19; 314,08</t>
+          <t>148,04; 313,66</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>69,44; 194,28</t>
+          <t>82,07; 173,28</t>
         </is>
       </c>
     </row>
